--- a/Excel Assignment 1 - Data Exploration.xlsx
+++ b/Excel Assignment 1 - Data Exploration.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vikne\Desktop\excel class\Assignment 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBC32A9B-12D2-4B4E-8AA5-E1AADAD6D0BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D690A5E1-C873-465D-BD97-FE26C716DF24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -141,19 +141,7 @@
     <t>Formula :</t>
   </si>
   <si>
-    <t>selling price   F2=E2*D2</t>
-  </si>
-  <si>
-    <t>Total selling price  F36=SUM([Total Price ($)])</t>
-  </si>
-  <si>
-    <t>selling price   B36 =COUNTA([Product Name])</t>
-  </si>
-  <si>
     <t>Average</t>
-  </si>
-  <si>
-    <t>Average =AVERAGE(Table1[Total Price ($)])</t>
   </si>
   <si>
     <t>* Howmany products in exist</t>
@@ -376,13 +364,25 @@
   <si>
     <t>Max Price = MAX(Table1[Total Price ($)])</t>
   </si>
+  <si>
+    <t>selling price   I2=H2*G2</t>
+  </si>
+  <si>
+    <t>Total selling price  I34=SUM([Selling Price ($)])</t>
+  </si>
+  <si>
+    <t>selling price   E34 =COUNTA([Product Name])</t>
+  </si>
+  <si>
+    <t>Average =AVERAGE(Table1[Selling Price ($)])</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -650,48 +650,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -713,11 +674,84 @@
     <xf numFmtId="1" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="27">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE0F7FA"/>
+          <bgColor rgb="FFE0F7FA"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -752,6 +786,42 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE0F7FA"/>
+          <bgColor rgb="FFE0F7FA"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -810,6 +880,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFE0F7FA"/>
@@ -820,7 +891,9 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -841,9 +914,9 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Arial"/>
-        <family val="2"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFE0F7FA"/>
@@ -854,50 +927,13 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE0F7FA"/>
-          <bgColor rgb="FFE0F7FA"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -928,251 +964,6 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE0F7FA"/>
-          <bgColor rgb="FFE0F7FA"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE0F7FA"/>
-          <bgColor rgb="FFE0F7FA"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE0F7FA"/>
-          <bgColor rgb="FFE0F7FA"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE0F7FA"/>
-          <bgColor rgb="FFE0F7FA"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE0F7FA"/>
-          <bgColor rgb="FFE0F7FA"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE0F7FA"/>
-          <bgColor rgb="FFE0F7FA"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE0F7FA"/>
-          <bgColor rgb="FFE0F7FA"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
         <right style="thin">
           <color indexed="64"/>
         </right>
@@ -1234,9 +1025,10 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Arial"/>
+        <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0"/>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFE0F7FA"/>
@@ -1247,13 +1039,13 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -1272,7 +1064,7 @@
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0"/>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFE0F7FA"/>
@@ -1292,6 +1084,42 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE0F7FA"/>
+          <bgColor rgb="FFE0F7FA"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -1347,6 +1175,42 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE0F7FA"/>
+          <bgColor rgb="FFE0F7FA"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
@@ -1368,6 +1232,40 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE0F7FA"/>
+          <bgColor rgb="FFE0F7FA"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -1421,6 +1319,40 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE0F7FA"/>
+          <bgColor rgb="FFE0F7FA"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
@@ -1442,6 +1374,40 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE0F7FA"/>
+          <bgColor rgb="FFE0F7FA"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -1493,6 +1459,40 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE0F7FA"/>
+          <bgColor rgb="FFE0F7FA"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
         <scheme val="none"/>
       </font>
       <fill>
@@ -1622,35 +1622,35 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DEF49E3B-527A-4719-87E7-39B5BF573FD8}" name="Table13" displayName="Table13" ref="A1:K34" totalsRowCount="1" headerRowDxfId="26" dataDxfId="24" headerRowBorderDxfId="25" tableBorderDxfId="23" totalsRowBorderDxfId="22">
   <autoFilter ref="A1:K33" xr:uid="{DEF49E3B-527A-4719-87E7-39B5BF573FD8}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{3DE7B53B-0E11-4B9F-9338-F3D97E973300}" name="Product ID" dataDxfId="21" totalsRowDxfId="12"/>
-    <tableColumn id="9" xr3:uid="{1FB1171A-8CAF-4627-A7D0-F6048F7564B9}" name="Day" dataDxfId="20" totalsRowDxfId="11">
+    <tableColumn id="1" xr3:uid="{3DE7B53B-0E11-4B9F-9338-F3D97E973300}" name="Product ID" dataDxfId="21" totalsRowDxfId="20"/>
+    <tableColumn id="9" xr3:uid="{1FB1171A-8CAF-4627-A7D0-F6048F7564B9}" name="Day" dataDxfId="19" totalsRowDxfId="18">
       <calculatedColumnFormula>LEFT(Table13[[#This Row],[Product ID]],2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{1959542B-5ED3-4CFB-8547-17F11FA046CB}" name="Country Code" dataDxfId="19" totalsRowDxfId="10">
+    <tableColumn id="10" xr3:uid="{1959542B-5ED3-4CFB-8547-17F11FA046CB}" name="Country Code" dataDxfId="17" totalsRowDxfId="16">
       <calculatedColumnFormula>RIGHT(Table13[[#This Row],[Product ID]],2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{3BAE4752-D330-4DFA-BAC3-947E13B755ED}" name="Month" dataDxfId="18" totalsRowDxfId="9">
+    <tableColumn id="11" xr3:uid="{3BAE4752-D330-4DFA-BAC3-947E13B755ED}" name="Month" dataDxfId="15" totalsRowDxfId="14">
       <calculatedColumnFormula>MID(Table13[[#This Row],[Product ID]],4,3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{CEE37F03-4FED-4761-BF0A-23066DFED529}" name="Product Name" totalsRowFunction="custom" dataDxfId="17" totalsRowDxfId="8">
+    <tableColumn id="2" xr3:uid="{CEE37F03-4FED-4761-BF0A-23066DFED529}" name="Product Name" totalsRowFunction="custom" dataDxfId="13" totalsRowDxfId="12">
       <calculatedColumnFormula>PROPER(TRIM(CLEAN(Table13[[#This Row],[Product Name]])))</calculatedColumnFormula>
       <totalsRowFormula>COUNTA(Table13[Product Name])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{602BD542-E6B1-4A8F-B59B-73C6E8714D06}" name="Brand Name" dataDxfId="16" totalsRowDxfId="7">
+    <tableColumn id="3" xr3:uid="{602BD542-E6B1-4A8F-B59B-73C6E8714D06}" name="Brand Name" dataDxfId="11" totalsRowDxfId="10">
       <calculatedColumnFormula>PROPER(TRIM(CLEAN(Table13[[#This Row],[Brand Name]])))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{D2776BEE-949E-469E-A097-161E6A2A2241}" name="Price ($)" dataDxfId="15" totalsRowDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{2F9E9289-B231-48C8-AC09-DA517D6ED47D}" name="Quantity" totalsRowFunction="custom" dataDxfId="13" totalsRowDxfId="5">
+    <tableColumn id="4" xr3:uid="{D2776BEE-949E-469E-A097-161E6A2A2241}" name="Price ($)" dataDxfId="9" totalsRowDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{2F9E9289-B231-48C8-AC09-DA517D6ED47D}" name="Quantity" totalsRowFunction="custom" dataDxfId="7" totalsRowDxfId="6">
       <totalsRowFormula>SUM(Table13[Quantity])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{387D842F-F46E-4365-8431-B8691E2B7476}" name="Selling Price ($)" totalsRowFunction="custom" dataDxfId="14" totalsRowDxfId="4">
+    <tableColumn id="6" xr3:uid="{387D842F-F46E-4365-8431-B8691E2B7476}" name="Selling Price ($)" totalsRowFunction="custom" dataDxfId="5" totalsRowDxfId="4">
       <calculatedColumnFormula>H2*G2</calculatedColumnFormula>
       <totalsRowFormula>SUM(Table13[Selling Price ($)])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{32B12BF8-6787-4461-A5F7-F43367DA1997}" name="Price Range($)" dataDxfId="1" totalsRowDxfId="3">
+    <tableColumn id="8" xr3:uid="{32B12BF8-6787-4461-A5F7-F43367DA1997}" name="Price Range($)" dataDxfId="3" totalsRowDxfId="2">
       <calculatedColumnFormula>IF(Table13[[#This Row],[Selling Price ($)]]&gt;=500,"HIGH","STANDARD")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{0CEF9099-E997-404B-999F-7483F9E35A81}" name="Category" dataDxfId="0" totalsRowDxfId="2">
+    <tableColumn id="7" xr3:uid="{0CEF9099-E997-404B-999F-7483F9E35A81}" name="Category" dataDxfId="1" totalsRowDxfId="0">
       <calculatedColumnFormula>PROPER(TRIM(CLEAN(Table13[[#This Row],[Category]])))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1863,11 +1863,12 @@
     <col min="3" max="5" width="20.88671875" customWidth="1"/>
     <col min="6" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="17.33203125" customWidth="1"/>
-    <col min="8" max="8" width="23.44140625" customWidth="1"/>
+    <col min="8" max="8" width="27" customWidth="1"/>
     <col min="9" max="9" width="27.44140625" customWidth="1"/>
     <col min="10" max="10" width="27.21875" customWidth="1"/>
     <col min="11" max="11" width="17.44140625" customWidth="1"/>
     <col min="16" max="16" width="30.109375" customWidth="1"/>
+    <col min="23" max="23" width="12.6640625" customWidth="1"/>
     <col min="26" max="26" width="52.33203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1876,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>1</v>
@@ -1897,10 +1898,10 @@
         <v>4</v>
       </c>
       <c r="I1" s="20" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="K1" s="6" t="s">
         <v>5</v>
@@ -1911,33 +1912,33 @@
       <c r="A2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="39" t="str">
+      <c r="B2" s="26" t="str">
         <f>LEFT(Table13[[#This Row],[Product ID]],2)</f>
         <v>28</v>
       </c>
-      <c r="C2" s="41" t="str">
+      <c r="C2" s="28" t="str">
         <f>RIGHT(Table13[[#This Row],[Product ID]],2)</f>
         <v>US</v>
       </c>
-      <c r="D2" s="41" t="str">
+      <c r="D2" s="28" t="str">
         <f>MID(Table13[[#This Row],[Product ID]],4,3)</f>
         <v>JAN</v>
       </c>
-      <c r="E2" s="43" t="str">
+      <c r="E2" s="30" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Product Name]])))</f>
         <v>Laptop</v>
       </c>
-      <c r="F2" s="43" t="str">
+      <c r="F2" s="30" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Brand Name]])))</f>
         <v>Dell</v>
       </c>
-      <c r="G2" s="36">
+      <c r="G2" s="23">
         <v>1000</v>
       </c>
       <c r="H2" s="16">
         <v>30</v>
       </c>
-      <c r="I2" s="36">
+      <c r="I2" s="23">
         <f t="shared" ref="I2:I33" si="0">H2*G2</f>
         <v>30000</v>
       </c>
@@ -1945,47 +1946,43 @@
         <f>IF(Table13[[#This Row],[Selling Price ($)]]&gt;=500,"HIGH","STANDARD")</f>
         <v>HIGH</v>
       </c>
-      <c r="K2" s="46" t="str">
+      <c r="K2" s="33" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Category]])))</f>
         <v>Electronics</v>
       </c>
       <c r="L2" s="2"/>
-      <c r="S2">
-        <f ca="1">COUNTIF(Table13[Brand Name],Table13[Price ($)]&lt;=100)</f>
-        <v>0</v>
-      </c>
     </row>
     <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="40" t="str">
+      <c r="B3" s="27" t="str">
         <f>LEFT(Table13[[#This Row],[Product ID]],2)</f>
         <v>15</v>
       </c>
-      <c r="C3" s="42" t="str">
+      <c r="C3" s="29" t="str">
         <f>RIGHT(Table13[[#This Row],[Product ID]],2)</f>
         <v>US</v>
       </c>
-      <c r="D3" s="42" t="str">
+      <c r="D3" s="29" t="str">
         <f>MID(Table13[[#This Row],[Product ID]],4,3)</f>
         <v>FEB</v>
       </c>
-      <c r="E3" s="44" t="str">
+      <c r="E3" s="31" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Product Name]])))</f>
         <v>Sneakers</v>
       </c>
-      <c r="F3" s="44" t="str">
+      <c r="F3" s="31" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Brand Name]])))</f>
         <v>Nike</v>
       </c>
-      <c r="G3" s="37">
+      <c r="G3" s="24">
         <v>80</v>
       </c>
       <c r="H3" s="17">
         <v>15</v>
       </c>
-      <c r="I3" s="37">
+      <c r="I3" s="24">
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
@@ -1993,46 +1990,46 @@
         <f>IF(Table13[[#This Row],[Selling Price ($)]]&gt;=500,"HIGH","STANDARD")</f>
         <v>HIGH</v>
       </c>
-      <c r="K3" s="46" t="str">
+      <c r="K3" s="33" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Category]])))</f>
         <v>Fashion</v>
       </c>
       <c r="L3" s="2"/>
       <c r="M3" s="10" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="39" t="str">
+      <c r="B4" s="26" t="str">
         <f>LEFT(Table13[[#This Row],[Product ID]],2)</f>
         <v>03</v>
       </c>
-      <c r="C4" s="41" t="str">
+      <c r="C4" s="28" t="str">
         <f>RIGHT(Table13[[#This Row],[Product ID]],2)</f>
         <v>US</v>
       </c>
-      <c r="D4" s="41" t="str">
+      <c r="D4" s="28" t="str">
         <f>MID(Table13[[#This Row],[Product ID]],4,3)</f>
         <v>MAR</v>
       </c>
-      <c r="E4" s="43" t="str">
+      <c r="E4" s="30" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Product Name]])))</f>
         <v>Coffee Maker</v>
       </c>
-      <c r="F4" s="43" t="str">
+      <c r="F4" s="30" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Brand Name]])))</f>
         <v>Keurig</v>
       </c>
-      <c r="G4" s="36">
+      <c r="G4" s="23">
         <v>130</v>
       </c>
       <c r="H4" s="16">
         <v>40</v>
       </c>
-      <c r="I4" s="36">
+      <c r="I4" s="23">
         <f t="shared" si="0"/>
         <v>5200</v>
       </c>
@@ -2040,7 +2037,7 @@
         <f>IF(Table13[[#This Row],[Selling Price ($)]]&gt;=500,"HIGH","STANDARD")</f>
         <v>HIGH</v>
       </c>
-      <c r="K4" s="46" t="str">
+      <c r="K4" s="33" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Category]])))</f>
         <v>Kitchen</v>
       </c>
@@ -2050,33 +2047,33 @@
       <c r="A5" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="40" t="str">
+      <c r="B5" s="27" t="str">
         <f>LEFT(Table13[[#This Row],[Product ID]],2)</f>
         <v>11</v>
       </c>
-      <c r="C5" s="42" t="str">
+      <c r="C5" s="29" t="str">
         <f>RIGHT(Table13[[#This Row],[Product ID]],2)</f>
         <v>US</v>
       </c>
-      <c r="D5" s="42" t="str">
+      <c r="D5" s="29" t="str">
         <f>MID(Table13[[#This Row],[Product ID]],4,3)</f>
         <v>APR</v>
       </c>
-      <c r="E5" s="44" t="str">
+      <c r="E5" s="31" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Product Name]])))</f>
         <v>Smartphone</v>
       </c>
-      <c r="F5" s="44" t="str">
+      <c r="F5" s="31" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Brand Name]])))</f>
         <v>Samsung</v>
       </c>
-      <c r="G5" s="37">
+      <c r="G5" s="24">
         <v>900</v>
       </c>
       <c r="H5" s="17">
         <v>25</v>
       </c>
-      <c r="I5" s="37">
+      <c r="I5" s="24">
         <f t="shared" si="0"/>
         <v>22500</v>
       </c>
@@ -2084,50 +2081,50 @@
         <f>IF(Table13[[#This Row],[Selling Price ($)]]&gt;=500,"HIGH","STANDARD")</f>
         <v>HIGH</v>
       </c>
-      <c r="K5" s="46" t="str">
+      <c r="K5" s="33" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Category]])))</f>
         <v>Electronics</v>
       </c>
       <c r="L5" s="2"/>
-      <c r="M5" s="33" t="s">
-        <v>67</v>
-      </c>
-      <c r="N5" s="34"/>
-      <c r="O5" s="34"/>
-      <c r="P5" s="34"/>
-      <c r="Q5" s="34"/>
+      <c r="M5" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="N5" s="38"/>
+      <c r="O5" s="38"/>
+      <c r="P5" s="38"/>
+      <c r="Q5" s="38"/>
     </row>
     <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="39" t="str">
+      <c r="B6" s="26" t="str">
         <f>LEFT(Table13[[#This Row],[Product ID]],2)</f>
         <v>22</v>
       </c>
-      <c r="C6" s="41" t="str">
+      <c r="C6" s="28" t="str">
         <f>RIGHT(Table13[[#This Row],[Product ID]],2)</f>
         <v>US</v>
       </c>
-      <c r="D6" s="41" t="str">
+      <c r="D6" s="28" t="str">
         <f>MID(Table13[[#This Row],[Product ID]],4,3)</f>
         <v>MAY</v>
       </c>
-      <c r="E6" s="43" t="str">
+      <c r="E6" s="30" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Product Name]])))</f>
         <v>Backpack</v>
       </c>
-      <c r="F6" s="43" t="str">
+      <c r="F6" s="30" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Brand Name]])))</f>
         <v>North Face</v>
       </c>
-      <c r="G6" s="36">
+      <c r="G6" s="23">
         <v>70</v>
       </c>
       <c r="H6" s="16">
         <v>20</v>
       </c>
-      <c r="I6" s="36">
+      <c r="I6" s="23">
         <f t="shared" si="0"/>
         <v>1400</v>
       </c>
@@ -2135,48 +2132,48 @@
         <f>IF(Table13[[#This Row],[Selling Price ($)]]&gt;=500,"HIGH","STANDARD")</f>
         <v>HIGH</v>
       </c>
-      <c r="K6" s="46" t="str">
+      <c r="K6" s="33" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Category]])))</f>
         <v>Outdoor</v>
       </c>
       <c r="L6" s="2"/>
-      <c r="M6" s="34"/>
-      <c r="N6" s="34"/>
-      <c r="O6" s="34"/>
-      <c r="P6" s="34"/>
-      <c r="Q6" s="34"/>
+      <c r="M6" s="38"/>
+      <c r="N6" s="38"/>
+      <c r="O6" s="38"/>
+      <c r="P6" s="38"/>
+      <c r="Q6" s="38"/>
     </row>
     <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="40" t="str">
+      <c r="B7" s="27" t="str">
         <f>LEFT(Table13[[#This Row],[Product ID]],2)</f>
         <v>07</v>
       </c>
-      <c r="C7" s="42" t="str">
+      <c r="C7" s="29" t="str">
         <f>RIGHT(Table13[[#This Row],[Product ID]],2)</f>
         <v>UK</v>
       </c>
-      <c r="D7" s="42" t="str">
+      <c r="D7" s="29" t="str">
         <f>MID(Table13[[#This Row],[Product ID]],4,3)</f>
         <v>JUN</v>
       </c>
-      <c r="E7" s="44" t="str">
+      <c r="E7" s="31" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Product Name]])))</f>
         <v>Headphones</v>
       </c>
-      <c r="F7" s="44" t="str">
+      <c r="F7" s="31" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Brand Name]])))</f>
         <v>Sony</v>
       </c>
-      <c r="G7" s="37">
+      <c r="G7" s="24">
         <v>200</v>
       </c>
       <c r="H7" s="17">
         <v>45</v>
       </c>
-      <c r="I7" s="37">
+      <c r="I7" s="24">
         <f t="shared" si="0"/>
         <v>9000</v>
       </c>
@@ -2184,49 +2181,49 @@
         <f>IF(Table13[[#This Row],[Selling Price ($)]]&gt;=500,"HIGH","STANDARD")</f>
         <v>HIGH</v>
       </c>
-      <c r="K7" s="46" t="str">
+      <c r="K7" s="33" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Category]])))</f>
         <v>Electronics</v>
       </c>
       <c r="L7" s="2"/>
-      <c r="N7" s="24" t="s">
+      <c r="N7" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="O7" s="24"/>
-      <c r="P7" s="24"/>
-      <c r="Q7" s="24"/>
+      <c r="O7" s="39"/>
+      <c r="P7" s="39"/>
+      <c r="Q7" s="39"/>
     </row>
     <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="39" t="str">
+      <c r="B8" s="26" t="str">
         <f>LEFT(Table13[[#This Row],[Product ID]],2)</f>
         <v>19</v>
       </c>
-      <c r="C8" s="41" t="str">
+      <c r="C8" s="28" t="str">
         <f>RIGHT(Table13[[#This Row],[Product ID]],2)</f>
         <v>UK</v>
       </c>
-      <c r="D8" s="41" t="str">
+      <c r="D8" s="28" t="str">
         <f>MID(Table13[[#This Row],[Product ID]],4,3)</f>
         <v>JUL</v>
       </c>
-      <c r="E8" s="43" t="str">
+      <c r="E8" s="30" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Product Name]])))</f>
         <v>T-Shirt</v>
       </c>
-      <c r="F8" s="43" t="str">
+      <c r="F8" s="30" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Brand Name]])))</f>
         <v>Adidas</v>
       </c>
-      <c r="G8" s="36">
+      <c r="G8" s="23">
         <v>30</v>
       </c>
       <c r="H8" s="16">
         <v>5</v>
       </c>
-      <c r="I8" s="36">
+      <c r="I8" s="23">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
@@ -2234,52 +2231,52 @@
         <f>IF(Table13[[#This Row],[Selling Price ($)]]&gt;=500,"HIGH","STANDARD")</f>
         <v>STANDARD</v>
       </c>
-      <c r="K8" s="46" t="str">
+      <c r="K8" s="33" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Category]])))</f>
         <v>Fashion</v>
       </c>
       <c r="L8" s="2"/>
-      <c r="N8" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="O8" s="25"/>
-      <c r="P8" s="25"/>
-      <c r="Q8" s="25"/>
+      <c r="N8" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="O8" s="35"/>
+      <c r="P8" s="35"/>
+      <c r="Q8" s="35"/>
       <c r="S8" s="14" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="40" t="str">
+      <c r="B9" s="27" t="str">
         <f>LEFT(Table13[[#This Row],[Product ID]],2)</f>
         <v>23</v>
       </c>
-      <c r="C9" s="42" t="str">
+      <c r="C9" s="29" t="str">
         <f>RIGHT(Table13[[#This Row],[Product ID]],2)</f>
         <v>UK</v>
       </c>
-      <c r="D9" s="42" t="str">
+      <c r="D9" s="29" t="str">
         <f>MID(Table13[[#This Row],[Product ID]],4,3)</f>
         <v>AUG</v>
       </c>
-      <c r="E9" s="44" t="str">
+      <c r="E9" s="31" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Product Name]])))</f>
         <v>Blender</v>
       </c>
-      <c r="F9" s="44" t="str">
+      <c r="F9" s="31" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Brand Name]])))</f>
         <v>Ninja</v>
       </c>
-      <c r="G9" s="37">
+      <c r="G9" s="24">
         <v>90</v>
       </c>
       <c r="H9" s="17">
         <v>35</v>
       </c>
-      <c r="I9" s="37">
+      <c r="I9" s="24">
         <f t="shared" si="0"/>
         <v>3150</v>
       </c>
@@ -2287,49 +2284,49 @@
         <f>IF(Table13[[#This Row],[Selling Price ($)]]&gt;=500,"HIGH","STANDARD")</f>
         <v>HIGH</v>
       </c>
-      <c r="K9" s="46" t="str">
+      <c r="K9" s="33" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Category]])))</f>
         <v>Kitchen</v>
       </c>
       <c r="L9" s="2"/>
-      <c r="N9" s="35" t="s">
-        <v>39</v>
-      </c>
-      <c r="O9" s="35"/>
-      <c r="P9" s="35"/>
-      <c r="Q9" s="35"/>
+      <c r="N9" s="40" t="s">
+        <v>71</v>
+      </c>
+      <c r="O9" s="40"/>
+      <c r="P9" s="40"/>
+      <c r="Q9" s="40"/>
     </row>
     <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="39" t="str">
+      <c r="B10" s="26" t="str">
         <f>LEFT(Table13[[#This Row],[Product ID]],2)</f>
         <v>05</v>
       </c>
-      <c r="C10" s="41" t="str">
+      <c r="C10" s="28" t="str">
         <f>RIGHT(Table13[[#This Row],[Product ID]],2)</f>
         <v>UK</v>
       </c>
-      <c r="D10" s="41" t="str">
+      <c r="D10" s="28" t="str">
         <f>MID(Table13[[#This Row],[Product ID]],4,3)</f>
         <v>SEP</v>
       </c>
-      <c r="E10" s="43" t="str">
+      <c r="E10" s="30" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Product Name]])))</f>
         <v>Tablet</v>
       </c>
-      <c r="F10" s="43" t="str">
+      <c r="F10" s="30" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Brand Name]])))</f>
         <v>Apple</v>
       </c>
-      <c r="G10" s="36">
+      <c r="G10" s="23">
         <v>500</v>
       </c>
       <c r="H10" s="16">
         <v>50</v>
       </c>
-      <c r="I10" s="36">
+      <c r="I10" s="23">
         <f t="shared" si="0"/>
         <v>25000</v>
       </c>
@@ -2337,60 +2334,59 @@
         <f>IF(Table13[[#This Row],[Selling Price ($)]]&gt;=500,"HIGH","STANDARD")</f>
         <v>HIGH</v>
       </c>
-      <c r="K10" s="46" t="str">
+      <c r="K10" s="33" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Category]])))</f>
         <v>Electronics</v>
       </c>
       <c r="L10" s="2"/>
-      <c r="N10" s="27">
-        <f>Table13[[#Totals],[Selling Price ($)]]</f>
+      <c r="N10" s="41">
         <v>264200</v>
       </c>
-      <c r="O10" s="27"/>
-      <c r="P10" s="27"/>
-      <c r="Q10" s="27"/>
-      <c r="S10" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="T10" s="28"/>
-      <c r="U10" s="28"/>
-      <c r="V10" s="28"/>
-      <c r="W10" s="28"/>
-      <c r="X10" s="28"/>
-      <c r="Y10" s="28"/>
-      <c r="Z10" s="28"/>
+      <c r="O10" s="41"/>
+      <c r="P10" s="41"/>
+      <c r="Q10" s="41"/>
+      <c r="S10" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="T10" s="36"/>
+      <c r="U10" s="36"/>
+      <c r="V10" s="36"/>
+      <c r="W10" s="36"/>
+      <c r="X10" s="36"/>
+      <c r="Y10" s="36"/>
+      <c r="Z10" s="36"/>
     </row>
     <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="40" t="str">
+      <c r="B11" s="27" t="str">
         <f>LEFT(Table13[[#This Row],[Product ID]],2)</f>
         <v>14</v>
       </c>
-      <c r="C11" s="42" t="str">
+      <c r="C11" s="29" t="str">
         <f>RIGHT(Table13[[#This Row],[Product ID]],2)</f>
         <v>UK</v>
       </c>
-      <c r="D11" s="42" t="str">
+      <c r="D11" s="29" t="str">
         <f>MID(Table13[[#This Row],[Product ID]],4,3)</f>
         <v>OCT</v>
       </c>
-      <c r="E11" s="44" t="str">
+      <c r="E11" s="31" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Product Name]])))</f>
         <v>Hiking Boots</v>
       </c>
-      <c r="F11" s="44" t="str">
+      <c r="F11" s="31" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Brand Name]])))</f>
         <v>Timberland</v>
       </c>
-      <c r="G11" s="37">
+      <c r="G11" s="24">
         <v>130</v>
       </c>
       <c r="H11" s="17">
         <v>10</v>
       </c>
-      <c r="I11" s="37">
+      <c r="I11" s="24">
         <f t="shared" si="0"/>
         <v>1300</v>
       </c>
@@ -2398,52 +2394,52 @@
         <f>IF(Table13[[#This Row],[Selling Price ($)]]&gt;=500,"HIGH","STANDARD")</f>
         <v>HIGH</v>
       </c>
-      <c r="K11" s="46" t="str">
+      <c r="K11" s="33" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Category]])))</f>
         <v>Outdoor</v>
       </c>
       <c r="L11" s="2"/>
-      <c r="T11" s="24" t="s">
+      <c r="T11" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="U11" s="24"/>
-      <c r="V11" s="24"/>
-      <c r="W11" s="24"/>
-      <c r="X11" s="24"/>
-      <c r="Y11" s="24"/>
-      <c r="Z11" s="24"/>
+      <c r="U11" s="39"/>
+      <c r="V11" s="39"/>
+      <c r="W11" s="39"/>
+      <c r="X11" s="39"/>
+      <c r="Y11" s="39"/>
+      <c r="Z11" s="39"/>
     </row>
     <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="39" t="str">
+      <c r="B12" s="26" t="str">
         <f>LEFT(Table13[[#This Row],[Product ID]],2)</f>
         <v>17</v>
       </c>
-      <c r="C12" s="41" t="str">
+      <c r="C12" s="28" t="str">
         <f>RIGHT(Table13[[#This Row],[Product ID]],2)</f>
         <v>IN</v>
       </c>
-      <c r="D12" s="41" t="str">
+      <c r="D12" s="28" t="str">
         <f>MID(Table13[[#This Row],[Product ID]],4,3)</f>
         <v>JUN</v>
       </c>
-      <c r="E12" s="43" t="str">
+      <c r="E12" s="30" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Product Name]])))</f>
         <v>Laptop</v>
       </c>
-      <c r="F12" s="43" t="str">
+      <c r="F12" s="30" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Brand Name]])))</f>
         <v>Hp</v>
       </c>
-      <c r="G12" s="36">
+      <c r="G12" s="23">
         <v>950</v>
       </c>
       <c r="H12" s="16">
         <v>25</v>
       </c>
-      <c r="I12" s="36">
+      <c r="I12" s="23">
         <f t="shared" si="0"/>
         <v>23750</v>
       </c>
@@ -2451,53 +2447,53 @@
         <f>IF(Table13[[#This Row],[Selling Price ($)]]&gt;=500,"HIGH","STANDARD")</f>
         <v>HIGH</v>
       </c>
-      <c r="K12" s="46" t="str">
+      <c r="K12" s="33" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Category]])))</f>
         <v>Electronics</v>
       </c>
       <c r="L12" s="2"/>
-      <c r="T12" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="U12" s="31"/>
-      <c r="V12" s="31"/>
-      <c r="W12" s="31"/>
-      <c r="X12" s="31"/>
-      <c r="Y12" s="31"/>
-      <c r="Z12" s="31"/>
+      <c r="T12" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="U12" s="42"/>
+      <c r="V12" s="42"/>
+      <c r="W12" s="42"/>
+      <c r="X12" s="42"/>
+      <c r="Y12" s="42"/>
+      <c r="Z12" s="42"/>
       <c r="AA12" s="15"/>
     </row>
     <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="40" t="str">
+      <c r="B13" s="27" t="str">
         <f>LEFT(Table13[[#This Row],[Product ID]],2)</f>
         <v>25</v>
       </c>
-      <c r="C13" s="42" t="str">
+      <c r="C13" s="29" t="str">
         <f>RIGHT(Table13[[#This Row],[Product ID]],2)</f>
         <v>AU</v>
       </c>
-      <c r="D13" s="42" t="str">
+      <c r="D13" s="29" t="str">
         <f>MID(Table13[[#This Row],[Product ID]],4,3)</f>
         <v>NOV</v>
       </c>
-      <c r="E13" s="44" t="str">
+      <c r="E13" s="31" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Product Name]])))</f>
         <v>Sneakers</v>
       </c>
-      <c r="F13" s="44" t="str">
+      <c r="F13" s="31" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Brand Name]])))</f>
         <v>Adidas</v>
       </c>
-      <c r="G13" s="37">
+      <c r="G13" s="24">
         <v>90</v>
       </c>
       <c r="H13" s="17">
         <v>40</v>
       </c>
-      <c r="I13" s="37">
+      <c r="I13" s="24">
         <f t="shared" si="0"/>
         <v>3600</v>
       </c>
@@ -2505,60 +2501,59 @@
         <f>IF(Table13[[#This Row],[Selling Price ($)]]&gt;=500,"HIGH","STANDARD")</f>
         <v>HIGH</v>
       </c>
-      <c r="K13" s="46" t="str">
+      <c r="K13" s="33" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Category]])))</f>
         <v>Fashion</v>
       </c>
       <c r="L13" s="2"/>
-      <c r="M13" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="T13" s="32">
-        <f ca="1">I44</f>
+      <c r="M13" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="N13" s="43"/>
+      <c r="O13" s="43"/>
+      <c r="P13" s="43"/>
+      <c r="Q13" s="43"/>
+      <c r="T13" s="44">
         <v>210450</v>
       </c>
-      <c r="U13" s="32"/>
-      <c r="V13" s="32"/>
-      <c r="W13" s="32"/>
-      <c r="X13" s="32"/>
-      <c r="Y13" s="32"/>
-      <c r="Z13" s="32"/>
+      <c r="U13" s="44"/>
+      <c r="V13" s="44"/>
+      <c r="W13" s="44"/>
+      <c r="X13" s="44"/>
+      <c r="Y13" s="44"/>
+      <c r="Z13" s="44"/>
     </row>
     <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="39" t="str">
+      <c r="B14" s="26" t="str">
         <f>LEFT(Table13[[#This Row],[Product ID]],2)</f>
         <v>08</v>
       </c>
-      <c r="C14" s="41" t="str">
+      <c r="C14" s="28" t="str">
         <f>RIGHT(Table13[[#This Row],[Product ID]],2)</f>
         <v>DE</v>
       </c>
-      <c r="D14" s="41" t="str">
+      <c r="D14" s="28" t="str">
         <f>MID(Table13[[#This Row],[Product ID]],4,3)</f>
         <v>DEC</v>
       </c>
-      <c r="E14" s="43" t="str">
+      <c r="E14" s="30" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Product Name]])))</f>
         <v>Coffee Maker</v>
       </c>
-      <c r="F14" s="43" t="str">
+      <c r="F14" s="30" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Brand Name]])))</f>
         <v>Nespresso</v>
       </c>
-      <c r="G14" s="36">
+      <c r="G14" s="23">
         <v>120</v>
       </c>
       <c r="H14" s="16">
         <v>35</v>
       </c>
-      <c r="I14" s="36">
+      <c r="I14" s="23">
         <f t="shared" si="0"/>
         <v>4200</v>
       </c>
@@ -2566,49 +2561,49 @@
         <f>IF(Table13[[#This Row],[Selling Price ($)]]&gt;=500,"HIGH","STANDARD")</f>
         <v>HIGH</v>
       </c>
-      <c r="K14" s="46" t="str">
+      <c r="K14" s="33" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Category]])))</f>
         <v>Kitchen</v>
       </c>
       <c r="L14" s="2"/>
-      <c r="N14" s="24" t="s">
+      <c r="N14" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="O14" s="24"/>
-      <c r="P14" s="24"/>
-      <c r="Q14" s="24"/>
+      <c r="O14" s="39"/>
+      <c r="P14" s="39"/>
+      <c r="Q14" s="39"/>
     </row>
     <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="40" t="str">
+      <c r="B15" s="27" t="str">
         <f>LEFT(Table13[[#This Row],[Product ID]],2)</f>
         <v>18</v>
       </c>
-      <c r="C15" s="42" t="str">
+      <c r="C15" s="29" t="str">
         <f>RIGHT(Table13[[#This Row],[Product ID]],2)</f>
         <v>CA</v>
       </c>
-      <c r="D15" s="42" t="str">
+      <c r="D15" s="29" t="str">
         <f>MID(Table13[[#This Row],[Product ID]],4,3)</f>
         <v>FEB</v>
       </c>
-      <c r="E15" s="44" t="str">
+      <c r="E15" s="31" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Product Name]])))</f>
         <v>Smartwatch</v>
       </c>
-      <c r="F15" s="44" t="str">
+      <c r="F15" s="31" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Brand Name]])))</f>
         <v>Fitbit</v>
       </c>
-      <c r="G15" s="37">
+      <c r="G15" s="24">
         <v>150</v>
       </c>
       <c r="H15" s="17">
         <v>15</v>
       </c>
-      <c r="I15" s="37">
+      <c r="I15" s="24">
         <f t="shared" si="0"/>
         <v>2250</v>
       </c>
@@ -2616,59 +2611,59 @@
         <f>IF(Table13[[#This Row],[Selling Price ($)]]&gt;=500,"HIGH","STANDARD")</f>
         <v>HIGH</v>
       </c>
-      <c r="K15" s="46" t="str">
+      <c r="K15" s="33" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Category]])))</f>
         <v>Electronics</v>
       </c>
       <c r="L15" s="2"/>
-      <c r="N15" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="O15" s="25"/>
-      <c r="P15" s="25"/>
-      <c r="Q15" s="25"/>
-      <c r="S15" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="T15" s="28"/>
-      <c r="U15" s="28"/>
-      <c r="V15" s="28"/>
-      <c r="W15" s="28"/>
-      <c r="X15" s="28"/>
-      <c r="Y15" s="28"/>
-      <c r="Z15" s="28"/>
+      <c r="N15" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="O15" s="35"/>
+      <c r="P15" s="35"/>
+      <c r="Q15" s="35"/>
+      <c r="S15" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="T15" s="36"/>
+      <c r="U15" s="36"/>
+      <c r="V15" s="36"/>
+      <c r="W15" s="36"/>
+      <c r="X15" s="36"/>
+      <c r="Y15" s="36"/>
+      <c r="Z15" s="36"/>
     </row>
     <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="39" t="str">
+      <c r="B16" s="26" t="str">
         <f>LEFT(Table13[[#This Row],[Product ID]],2)</f>
         <v>16</v>
       </c>
-      <c r="C16" s="41" t="str">
+      <c r="C16" s="28" t="str">
         <f>RIGHT(Table13[[#This Row],[Product ID]],2)</f>
         <v>ES</v>
       </c>
-      <c r="D16" s="41" t="str">
+      <c r="D16" s="28" t="str">
         <f>MID(Table13[[#This Row],[Product ID]],4,3)</f>
         <v>APR</v>
       </c>
-      <c r="E16" s="43" t="str">
+      <c r="E16" s="30" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Product Name]])))</f>
         <v>Headphones</v>
       </c>
-      <c r="F16" s="43" t="str">
+      <c r="F16" s="30" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Brand Name]])))</f>
         <v>Bose</v>
       </c>
-      <c r="G16" s="36">
+      <c r="G16" s="23">
         <v>250</v>
       </c>
       <c r="H16" s="16">
         <v>20</v>
       </c>
-      <c r="I16" s="36">
+      <c r="I16" s="23">
         <f t="shared" si="0"/>
         <v>5000</v>
       </c>
@@ -2676,59 +2671,58 @@
         <f>IF(Table13[[#This Row],[Selling Price ($)]]&gt;=500,"HIGH","STANDARD")</f>
         <v>HIGH</v>
       </c>
-      <c r="K16" s="46" t="str">
+      <c r="K16" s="33" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Category]])))</f>
         <v>Electronics</v>
       </c>
       <c r="L16" s="2"/>
-      <c r="N16" s="27">
-        <f ca="1">Table13[[#Totals],[Product Name]]</f>
+      <c r="N16" s="41">
         <v>32</v>
       </c>
-      <c r="O16" s="27"/>
-      <c r="P16" s="27"/>
-      <c r="Q16" s="27"/>
-      <c r="T16" s="24" t="s">
+      <c r="O16" s="41"/>
+      <c r="P16" s="41"/>
+      <c r="Q16" s="41"/>
+      <c r="T16" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="U16" s="24"/>
-      <c r="V16" s="24"/>
-      <c r="W16" s="24"/>
-      <c r="X16" s="24"/>
-      <c r="Y16" s="24"/>
-      <c r="Z16" s="24"/>
+      <c r="U16" s="39"/>
+      <c r="V16" s="39"/>
+      <c r="W16" s="39"/>
+      <c r="X16" s="39"/>
+      <c r="Y16" s="39"/>
+      <c r="Z16" s="39"/>
     </row>
     <row r="17" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="40" t="str">
+      <c r="B17" s="27" t="str">
         <f>LEFT(Table13[[#This Row],[Product ID]],2)</f>
         <v>21</v>
       </c>
-      <c r="C17" s="42" t="str">
+      <c r="C17" s="29" t="str">
         <f>RIGHT(Table13[[#This Row],[Product ID]],2)</f>
         <v>CA</v>
       </c>
-      <c r="D17" s="42" t="str">
+      <c r="D17" s="29" t="str">
         <f>MID(Table13[[#This Row],[Product ID]],4,3)</f>
         <v>AUG</v>
       </c>
-      <c r="E17" s="44" t="str">
+      <c r="E17" s="31" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Product Name]])))</f>
         <v>Laptop Bag</v>
       </c>
-      <c r="F17" s="44" t="str">
+      <c r="F17" s="31" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Brand Name]])))</f>
         <v>Samsonite</v>
       </c>
-      <c r="G17" s="37">
+      <c r="G17" s="24">
         <v>50</v>
       </c>
       <c r="H17" s="17">
         <v>35</v>
       </c>
-      <c r="I17" s="37">
+      <c r="I17" s="24">
         <f t="shared" si="0"/>
         <v>1750</v>
       </c>
@@ -2736,52 +2730,52 @@
         <f>IF(Table13[[#This Row],[Selling Price ($)]]&gt;=500,"HIGH","STANDARD")</f>
         <v>HIGH</v>
       </c>
-      <c r="K17" s="46" t="str">
+      <c r="K17" s="33" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Category]])))</f>
         <v>Accessories</v>
       </c>
       <c r="L17" s="2"/>
-      <c r="T17" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="U17" s="31"/>
-      <c r="V17" s="31"/>
-      <c r="W17" s="31"/>
-      <c r="X17" s="31"/>
-      <c r="Y17" s="31"/>
-      <c r="Z17" s="31"/>
+      <c r="T17" s="42" t="s">
+        <v>68</v>
+      </c>
+      <c r="U17" s="42"/>
+      <c r="V17" s="42"/>
+      <c r="W17" s="42"/>
+      <c r="X17" s="42"/>
+      <c r="Y17" s="42"/>
+      <c r="Z17" s="42"/>
     </row>
     <row r="18" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="39" t="str">
+      <c r="B18" s="26" t="str">
         <f>LEFT(Table13[[#This Row],[Product ID]],2)</f>
         <v>20</v>
       </c>
-      <c r="C18" s="41" t="str">
+      <c r="C18" s="28" t="str">
         <f>RIGHT(Table13[[#This Row],[Product ID]],2)</f>
         <v>CN</v>
       </c>
-      <c r="D18" s="41" t="str">
+      <c r="D18" s="28" t="str">
         <f>MID(Table13[[#This Row],[Product ID]],4,3)</f>
         <v>AUG</v>
       </c>
-      <c r="E18" s="43" t="str">
+      <c r="E18" s="30" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Product Name]])))</f>
         <v>Smartwatch</v>
       </c>
-      <c r="F18" s="43" t="str">
+      <c r="F18" s="30" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Brand Name]])))</f>
         <v>Huawei</v>
       </c>
-      <c r="G18" s="36">
+      <c r="G18" s="23">
         <v>160</v>
       </c>
       <c r="H18" s="16">
         <v>15</v>
       </c>
-      <c r="I18" s="36">
+      <c r="I18" s="23">
         <f t="shared" si="0"/>
         <v>2400</v>
       </c>
@@ -2789,60 +2783,59 @@
         <f>IF(Table13[[#This Row],[Selling Price ($)]]&gt;=500,"HIGH","STANDARD")</f>
         <v>HIGH</v>
       </c>
-      <c r="K18" s="46" t="str">
+      <c r="K18" s="33" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Category]])))</f>
         <v>Electronics</v>
       </c>
       <c r="L18" s="2"/>
-      <c r="M18" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
-      <c r="T18" s="32">
-        <f>I46</f>
+      <c r="M18" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="N18" s="43"/>
+      <c r="O18" s="43"/>
+      <c r="P18" s="43"/>
+      <c r="Q18" s="43"/>
+      <c r="T18" s="44">
         <v>11</v>
       </c>
-      <c r="U18" s="32"/>
-      <c r="V18" s="32"/>
-      <c r="W18" s="32"/>
-      <c r="X18" s="32"/>
-      <c r="Y18" s="32"/>
-      <c r="Z18" s="32"/>
+      <c r="U18" s="44"/>
+      <c r="V18" s="44"/>
+      <c r="W18" s="44"/>
+      <c r="X18" s="44"/>
+      <c r="Y18" s="44"/>
+      <c r="Z18" s="44"/>
     </row>
     <row r="19" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="40" t="str">
+      <c r="B19" s="27" t="str">
         <f>LEFT(Table13[[#This Row],[Product ID]],2)</f>
         <v>27</v>
       </c>
-      <c r="C19" s="42" t="str">
+      <c r="C19" s="29" t="str">
         <f>RIGHT(Table13[[#This Row],[Product ID]],2)</f>
         <v>IT</v>
       </c>
-      <c r="D19" s="42" t="str">
+      <c r="D19" s="29" t="str">
         <f>MID(Table13[[#This Row],[Product ID]],4,3)</f>
         <v>JAN</v>
       </c>
-      <c r="E19" s="44" t="str">
+      <c r="E19" s="31" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Product Name]])))</f>
         <v>Laptop</v>
       </c>
-      <c r="F19" s="44" t="str">
+      <c r="F19" s="31" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Brand Name]])))</f>
         <v>Asus</v>
       </c>
-      <c r="G19" s="37">
+      <c r="G19" s="24">
         <v>980</v>
       </c>
       <c r="H19" s="17">
         <v>10</v>
       </c>
-      <c r="I19" s="37">
+      <c r="I19" s="24">
         <f t="shared" si="0"/>
         <v>9800</v>
       </c>
@@ -2850,49 +2843,49 @@
         <f>IF(Table13[[#This Row],[Selling Price ($)]]&gt;=500,"HIGH","STANDARD")</f>
         <v>HIGH</v>
       </c>
-      <c r="K19" s="46" t="str">
+      <c r="K19" s="33" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Category]])))</f>
         <v>Electronics</v>
       </c>
       <c r="L19" s="2"/>
-      <c r="N19" s="24" t="s">
+      <c r="N19" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="O19" s="24"/>
-      <c r="P19" s="24"/>
-      <c r="Q19" s="24"/>
+      <c r="O19" s="39"/>
+      <c r="P19" s="39"/>
+      <c r="Q19" s="39"/>
     </row>
     <row r="20" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="39" t="str">
+      <c r="B20" s="26" t="str">
         <f>LEFT(Table13[[#This Row],[Product ID]],2)</f>
         <v>01</v>
       </c>
-      <c r="C20" s="41" t="str">
+      <c r="C20" s="28" t="str">
         <f>RIGHT(Table13[[#This Row],[Product ID]],2)</f>
         <v>UK</v>
       </c>
-      <c r="D20" s="41" t="str">
+      <c r="D20" s="28" t="str">
         <f>MID(Table13[[#This Row],[Product ID]],4,3)</f>
         <v>MAR</v>
       </c>
-      <c r="E20" s="43" t="str">
+      <c r="E20" s="30" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Product Name]])))</f>
         <v>Sunglasses</v>
       </c>
-      <c r="F20" s="43" t="str">
+      <c r="F20" s="30" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Brand Name]])))</f>
         <v>Oakley</v>
       </c>
-      <c r="G20" s="36">
+      <c r="G20" s="23">
         <v>150</v>
       </c>
       <c r="H20" s="16">
         <v>15</v>
       </c>
-      <c r="I20" s="36">
+      <c r="I20" s="23">
         <f t="shared" si="0"/>
         <v>2250</v>
       </c>
@@ -2900,49 +2893,49 @@
         <f>IF(Table13[[#This Row],[Selling Price ($)]]&gt;=500,"HIGH","STANDARD")</f>
         <v>HIGH</v>
       </c>
-      <c r="K20" s="46" t="str">
+      <c r="K20" s="33" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Category]])))</f>
         <v>Fashion</v>
       </c>
       <c r="L20" s="2"/>
-      <c r="N20" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="O20" s="25"/>
-      <c r="P20" s="25"/>
-      <c r="Q20" s="25"/>
+      <c r="N20" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="O20" s="35"/>
+      <c r="P20" s="35"/>
+      <c r="Q20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="40" t="str">
+      <c r="B21" s="27" t="str">
         <f>LEFT(Table13[[#This Row],[Product ID]],2)</f>
         <v>14</v>
       </c>
-      <c r="C21" s="42" t="str">
+      <c r="C21" s="29" t="str">
         <f>RIGHT(Table13[[#This Row],[Product ID]],2)</f>
         <v>US</v>
       </c>
-      <c r="D21" s="42" t="str">
+      <c r="D21" s="29" t="str">
         <f>MID(Table13[[#This Row],[Product ID]],4,3)</f>
         <v>AUG</v>
       </c>
-      <c r="E21" s="44" t="str">
+      <c r="E21" s="31" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Product Name]])))</f>
         <v>Camping Tent</v>
       </c>
-      <c r="F21" s="44" t="str">
+      <c r="F21" s="31" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Brand Name]])))</f>
         <v>Coleman</v>
       </c>
-      <c r="G21" s="37">
+      <c r="G21" s="24">
         <v>200</v>
       </c>
       <c r="H21" s="17">
         <v>10</v>
       </c>
-      <c r="I21" s="37">
+      <c r="I21" s="24">
         <f t="shared" si="0"/>
         <v>2000</v>
       </c>
@@ -2950,53 +2943,52 @@
         <f>IF(Table13[[#This Row],[Selling Price ($)]]&gt;=500,"HIGH","STANDARD")</f>
         <v>HIGH</v>
       </c>
-      <c r="K21" s="46" t="str">
+      <c r="K21" s="33" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Category]])))</f>
         <v>Outdoor</v>
       </c>
       <c r="L21" s="2"/>
-      <c r="N21" s="27">
-        <f>I38</f>
+      <c r="N21" s="41">
         <v>8256.25</v>
       </c>
-      <c r="O21" s="27"/>
-      <c r="P21" s="27"/>
-      <c r="Q21" s="27"/>
+      <c r="O21" s="41"/>
+      <c r="P21" s="41"/>
+      <c r="Q21" s="41"/>
       <c r="S21" s="14" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="39" t="str">
+      <c r="B22" s="26" t="str">
         <f>LEFT(Table13[[#This Row],[Product ID]],2)</f>
         <v>14</v>
       </c>
-      <c r="C22" s="41" t="str">
+      <c r="C22" s="28" t="str">
         <f>RIGHT(Table13[[#This Row],[Product ID]],2)</f>
         <v>RU</v>
       </c>
-      <c r="D22" s="41" t="str">
+      <c r="D22" s="28" t="str">
         <f>MID(Table13[[#This Row],[Product ID]],4,3)</f>
         <v>MAY</v>
       </c>
-      <c r="E22" s="43" t="str">
+      <c r="E22" s="30" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Product Name]])))</f>
         <v>Camera</v>
       </c>
-      <c r="F22" s="43" t="str">
+      <c r="F22" s="30" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Brand Name]])))</f>
         <v>Nikon</v>
       </c>
-      <c r="G22" s="36">
+      <c r="G22" s="23">
         <v>700</v>
       </c>
       <c r="H22" s="16">
         <v>50</v>
       </c>
-      <c r="I22" s="36">
+      <c r="I22" s="23">
         <f t="shared" si="0"/>
         <v>35000</v>
       </c>
@@ -3004,7 +2996,7 @@
         <f>IF(Table13[[#This Row],[Selling Price ($)]]&gt;=500,"HIGH","STANDARD")</f>
         <v>HIGH</v>
       </c>
-      <c r="K22" s="46" t="str">
+      <c r="K22" s="33" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Category]])))</f>
         <v>Electronics</v>
       </c>
@@ -3014,33 +3006,33 @@
       <c r="A23" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="40" t="str">
+      <c r="B23" s="27" t="str">
         <f>LEFT(Table13[[#This Row],[Product ID]],2)</f>
         <v>09</v>
       </c>
-      <c r="C23" s="42" t="str">
+      <c r="C23" s="29" t="str">
         <f>RIGHT(Table13[[#This Row],[Product ID]],2)</f>
         <v>CA</v>
       </c>
-      <c r="D23" s="42" t="str">
+      <c r="D23" s="29" t="str">
         <f>MID(Table13[[#This Row],[Product ID]],4,3)</f>
         <v>JAN</v>
       </c>
-      <c r="E23" s="44" t="str">
+      <c r="E23" s="31" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Product Name]])))</f>
         <v>Microwave</v>
       </c>
-      <c r="F23" s="44" t="str">
+      <c r="F23" s="31" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Brand Name]])))</f>
         <v>Panasonic</v>
       </c>
-      <c r="G23" s="37">
+      <c r="G23" s="24">
         <v>80</v>
       </c>
       <c r="H23" s="17">
         <v>20</v>
       </c>
-      <c r="I23" s="37">
+      <c r="I23" s="24">
         <f t="shared" si="0"/>
         <v>1600</v>
       </c>
@@ -3048,56 +3040,56 @@
         <f>IF(Table13[[#This Row],[Selling Price ($)]]&gt;=500,"HIGH","STANDARD")</f>
         <v>HIGH</v>
       </c>
-      <c r="K23" s="46" t="str">
+      <c r="K23" s="33" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Category]])))</f>
         <v>Kitchen</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="S23" s="28" t="s">
-        <v>66</v>
-      </c>
-      <c r="T23" s="29"/>
-      <c r="U23" s="29"/>
-      <c r="V23" s="29"/>
-      <c r="W23" s="29"/>
-      <c r="X23" s="29"/>
-      <c r="Y23" s="29"/>
-      <c r="Z23" s="29"/>
+        <v>42</v>
+      </c>
+      <c r="S23" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="T23" s="46"/>
+      <c r="U23" s="46"/>
+      <c r="V23" s="46"/>
+      <c r="W23" s="46"/>
+      <c r="X23" s="46"/>
+      <c r="Y23" s="46"/>
+      <c r="Z23" s="46"/>
     </row>
     <row r="24" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="39" t="str">
+      <c r="B24" s="26" t="str">
         <f>LEFT(Table13[[#This Row],[Product ID]],2)</f>
         <v>19</v>
       </c>
-      <c r="C24" s="41" t="str">
+      <c r="C24" s="28" t="str">
         <f>RIGHT(Table13[[#This Row],[Product ID]],2)</f>
         <v>BR</v>
       </c>
-      <c r="D24" s="41" t="str">
+      <c r="D24" s="28" t="str">
         <f>MID(Table13[[#This Row],[Product ID]],4,3)</f>
         <v>JUL</v>
       </c>
-      <c r="E24" s="43" t="str">
+      <c r="E24" s="30" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Product Name]])))</f>
         <v>Fitness Tracker</v>
       </c>
-      <c r="F24" s="43" t="str">
+      <c r="F24" s="30" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Brand Name]])))</f>
         <v>Xiaomi</v>
       </c>
-      <c r="G24" s="36">
+      <c r="G24" s="23">
         <v>150</v>
       </c>
       <c r="H24" s="16">
         <v>30</v>
       </c>
-      <c r="I24" s="36">
+      <c r="I24" s="23">
         <f t="shared" si="0"/>
         <v>4500</v>
       </c>
@@ -3105,52 +3097,52 @@
         <f>IF(Table13[[#This Row],[Selling Price ($)]]&gt;=500,"HIGH","STANDARD")</f>
         <v>HIGH</v>
       </c>
-      <c r="K24" s="46" t="str">
+      <c r="K24" s="33" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Category]])))</f>
         <v>Electronics</v>
       </c>
       <c r="L24" s="2"/>
-      <c r="T24" s="30" t="s">
-        <v>69</v>
-      </c>
-      <c r="U24" s="30"/>
-      <c r="V24" s="30"/>
-      <c r="W24" s="30"/>
-      <c r="X24" s="30"/>
-      <c r="Y24" s="30"/>
-      <c r="Z24" s="30"/>
+      <c r="T24" s="45" t="s">
+        <v>65</v>
+      </c>
+      <c r="U24" s="45"/>
+      <c r="V24" s="45"/>
+      <c r="W24" s="45"/>
+      <c r="X24" s="45"/>
+      <c r="Y24" s="45"/>
+      <c r="Z24" s="45"/>
     </row>
     <row r="25" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="39" t="str">
+      <c r="B25" s="26" t="str">
         <f>LEFT(Table13[[#This Row],[Product ID]],2)</f>
         <v>29</v>
       </c>
-      <c r="C25" s="41" t="str">
+      <c r="C25" s="28" t="str">
         <f>RIGHT(Table13[[#This Row],[Product ID]],2)</f>
         <v>CA</v>
       </c>
-      <c r="D25" s="41" t="str">
+      <c r="D25" s="28" t="str">
         <f>MID(Table13[[#This Row],[Product ID]],4,3)</f>
         <v>SEP</v>
       </c>
-      <c r="E25" s="43" t="str">
+      <c r="E25" s="30" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Product Name]])))</f>
         <v>Smartphone</v>
       </c>
-      <c r="F25" s="43" t="str">
+      <c r="F25" s="30" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Brand Name]])))</f>
         <v>Google</v>
       </c>
-      <c r="G25" s="36">
+      <c r="G25" s="23">
         <v>800</v>
       </c>
       <c r="H25" s="16">
         <v>45</v>
       </c>
-      <c r="I25" s="36">
+      <c r="I25" s="23">
         <f t="shared" si="0"/>
         <v>36000</v>
       </c>
@@ -3158,20 +3150,20 @@
         <f>IF(Table13[[#This Row],[Selling Price ($)]]&gt;=500,"HIGH","STANDARD")</f>
         <v>HIGH</v>
       </c>
-      <c r="K25" s="46" t="str">
+      <c r="K25" s="33" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Category]])))</f>
         <v>Electronics</v>
       </c>
       <c r="L25" s="3"/>
-      <c r="M25" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="N25" s="23"/>
-      <c r="O25" s="23"/>
-      <c r="P25" s="23"/>
-      <c r="Q25" s="23"/>
+      <c r="M25" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="N25" s="43"/>
+      <c r="O25" s="43"/>
+      <c r="P25" s="43"/>
+      <c r="Q25" s="43"/>
       <c r="T25" s="21" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="U25" s="21"/>
       <c r="V25" s="21"/>
@@ -3184,33 +3176,33 @@
       <c r="A26" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="40" t="str">
+      <c r="B26" s="27" t="str">
         <f>LEFT(Table13[[#This Row],[Product ID]],2)</f>
         <v>03</v>
       </c>
-      <c r="C26" s="42" t="str">
+      <c r="C26" s="29" t="str">
         <f>RIGHT(Table13[[#This Row],[Product ID]],2)</f>
         <v>CA</v>
       </c>
-      <c r="D26" s="42" t="str">
+      <c r="D26" s="29" t="str">
         <f>MID(Table13[[#This Row],[Product ID]],4,3)</f>
         <v>JUN</v>
       </c>
-      <c r="E26" s="44" t="str">
+      <c r="E26" s="31" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Product Name]])))</f>
         <v>Sunglasses</v>
       </c>
-      <c r="F26" s="44" t="str">
+      <c r="F26" s="31" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Brand Name]])))</f>
         <v>Ray-Ban</v>
       </c>
-      <c r="G26" s="37">
+      <c r="G26" s="24">
         <v>130</v>
       </c>
       <c r="H26" s="17">
         <v>25</v>
       </c>
-      <c r="I26" s="37">
+      <c r="I26" s="24">
         <f t="shared" si="0"/>
         <v>3250</v>
       </c>
@@ -3218,58 +3210,58 @@
         <f>IF(Table13[[#This Row],[Selling Price ($)]]&gt;=500,"HIGH","STANDARD")</f>
         <v>HIGH</v>
       </c>
-      <c r="K26" s="46" t="str">
+      <c r="K26" s="33" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Category]])))</f>
         <v>Fashion</v>
       </c>
       <c r="L26" s="2"/>
-      <c r="N26" s="24" t="s">
+      <c r="N26" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="O26" s="24"/>
-      <c r="P26" s="24"/>
-      <c r="Q26" s="24"/>
-      <c r="T26" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="U26" s="30"/>
-      <c r="V26" s="30"/>
-      <c r="W26" s="30"/>
-      <c r="X26" s="30"/>
-      <c r="Y26" s="30"/>
-      <c r="Z26" s="30"/>
+      <c r="O26" s="39"/>
+      <c r="P26" s="39"/>
+      <c r="Q26" s="39"/>
+      <c r="T26" s="45" t="s">
+        <v>66</v>
+      </c>
+      <c r="U26" s="45"/>
+      <c r="V26" s="45"/>
+      <c r="W26" s="45"/>
+      <c r="X26" s="45"/>
+      <c r="Y26" s="45"/>
+      <c r="Z26" s="45"/>
     </row>
     <row r="27" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B27" s="39" t="str">
+      <c r="B27" s="26" t="str">
         <f>LEFT(Table13[[#This Row],[Product ID]],2)</f>
         <v>11</v>
       </c>
-      <c r="C27" s="41" t="str">
+      <c r="C27" s="28" t="str">
         <f>RIGHT(Table13[[#This Row],[Product ID]],2)</f>
         <v>CA</v>
       </c>
-      <c r="D27" s="41" t="str">
+      <c r="D27" s="28" t="str">
         <f>MID(Table13[[#This Row],[Product ID]],4,3)</f>
         <v>JUL</v>
       </c>
-      <c r="E27" s="43" t="str">
+      <c r="E27" s="30" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Product Name]])))</f>
         <v>Blender</v>
       </c>
-      <c r="F27" s="43" t="str">
+      <c r="F27" s="30" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Brand Name]])))</f>
         <v>Vitamix</v>
       </c>
-      <c r="G27" s="36">
+      <c r="G27" s="23">
         <v>400</v>
       </c>
       <c r="H27" s="16">
         <v>40</v>
       </c>
-      <c r="I27" s="36">
+      <c r="I27" s="23">
         <f t="shared" si="0"/>
         <v>16000</v>
       </c>
@@ -3277,49 +3269,49 @@
         <f>IF(Table13[[#This Row],[Selling Price ($)]]&gt;=500,"HIGH","STANDARD")</f>
         <v>HIGH</v>
       </c>
-      <c r="K27" s="46" t="str">
+      <c r="K27" s="33" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Category]])))</f>
         <v>Kitchen</v>
       </c>
       <c r="L27" s="2"/>
-      <c r="N27" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="O27" s="25"/>
-      <c r="P27" s="25"/>
-      <c r="Q27" s="25"/>
+      <c r="N27" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="O27" s="35"/>
+      <c r="P27" s="35"/>
+      <c r="Q27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B28" s="40" t="str">
+      <c r="B28" s="27" t="str">
         <f>LEFT(Table13[[#This Row],[Product ID]],2)</f>
         <v>16</v>
       </c>
-      <c r="C28" s="42" t="str">
+      <c r="C28" s="29" t="str">
         <f>RIGHT(Table13[[#This Row],[Product ID]],2)</f>
         <v>ES</v>
       </c>
-      <c r="D28" s="42" t="str">
+      <c r="D28" s="29" t="str">
         <f>MID(Table13[[#This Row],[Product ID]],4,3)</f>
         <v>APR</v>
       </c>
-      <c r="E28" s="44" t="str">
+      <c r="E28" s="31" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Product Name]])))</f>
         <v>Headphones</v>
       </c>
-      <c r="F28" s="44" t="str">
+      <c r="F28" s="31" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Brand Name]])))</f>
         <v>Bose</v>
       </c>
-      <c r="G28" s="37">
+      <c r="G28" s="24">
         <v>230</v>
       </c>
       <c r="H28" s="17">
         <v>20</v>
       </c>
-      <c r="I28" s="37">
+      <c r="I28" s="24">
         <f t="shared" si="0"/>
         <v>4600</v>
       </c>
@@ -3327,50 +3319,49 @@
         <f>IF(Table13[[#This Row],[Selling Price ($)]]&gt;=500,"HIGH","STANDARD")</f>
         <v>HIGH</v>
       </c>
-      <c r="K28" s="46" t="str">
+      <c r="K28" s="33" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Category]])))</f>
         <v>Electronics</v>
       </c>
       <c r="L28" s="2"/>
-      <c r="N28" s="27">
-        <f>I40</f>
+      <c r="N28" s="41">
         <v>150</v>
       </c>
-      <c r="O28" s="27"/>
-      <c r="P28" s="27"/>
-      <c r="Q28" s="27"/>
+      <c r="O28" s="41"/>
+      <c r="P28" s="41"/>
+      <c r="Q28" s="41"/>
     </row>
     <row r="29" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="39" t="str">
+      <c r="B29" s="26" t="str">
         <f>LEFT(Table13[[#This Row],[Product ID]],2)</f>
         <v>07</v>
       </c>
-      <c r="C29" s="41" t="str">
+      <c r="C29" s="28" t="str">
         <f>RIGHT(Table13[[#This Row],[Product ID]],2)</f>
         <v>CA</v>
       </c>
-      <c r="D29" s="41" t="str">
+      <c r="D29" s="28" t="str">
         <f>MID(Table13[[#This Row],[Product ID]],4,3)</f>
         <v>MAR</v>
       </c>
-      <c r="E29" s="43" t="str">
+      <c r="E29" s="30" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Product Name]])))</f>
         <v>Dress</v>
       </c>
-      <c r="F29" s="43" t="str">
+      <c r="F29" s="30" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Brand Name]])))</f>
         <v>Zara</v>
       </c>
-      <c r="G29" s="36">
+      <c r="G29" s="23">
         <v>60</v>
       </c>
       <c r="H29" s="16">
         <v>30</v>
       </c>
-      <c r="I29" s="36">
+      <c r="I29" s="23">
         <f t="shared" si="0"/>
         <v>1800</v>
       </c>
@@ -3378,7 +3369,7 @@
         <f>IF(Table13[[#This Row],[Selling Price ($)]]&gt;=500,"HIGH","STANDARD")</f>
         <v>HIGH</v>
       </c>
-      <c r="K29" s="46" t="str">
+      <c r="K29" s="33" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Category]])))</f>
         <v>Fashion</v>
       </c>
@@ -3388,33 +3379,33 @@
       <c r="A30" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="40" t="str">
+      <c r="B30" s="27" t="str">
         <f>LEFT(Table13[[#This Row],[Product ID]],2)</f>
         <v>13</v>
       </c>
-      <c r="C30" s="42" t="str">
+      <c r="C30" s="29" t="str">
         <f>RIGHT(Table13[[#This Row],[Product ID]],2)</f>
         <v>CA</v>
       </c>
-      <c r="D30" s="42" t="str">
+      <c r="D30" s="29" t="str">
         <f>MID(Table13[[#This Row],[Product ID]],4,3)</f>
         <v>APR</v>
       </c>
-      <c r="E30" s="44" t="str">
+      <c r="E30" s="31" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Product Name]])))</f>
         <v>Toaster</v>
       </c>
-      <c r="F30" s="44" t="str">
+      <c r="F30" s="31" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Brand Name]])))</f>
         <v>Hamilton</v>
       </c>
-      <c r="G30" s="37">
+      <c r="G30" s="24">
         <v>40</v>
       </c>
       <c r="H30" s="17">
         <v>10</v>
       </c>
-      <c r="I30" s="37">
+      <c r="I30" s="24">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
@@ -3422,50 +3413,50 @@
         <f>IF(Table13[[#This Row],[Selling Price ($)]]&gt;=500,"HIGH","STANDARD")</f>
         <v>STANDARD</v>
       </c>
-      <c r="K30" s="46" t="str">
+      <c r="K30" s="33" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Category]])))</f>
         <v>Kitchen</v>
       </c>
       <c r="L30" s="2"/>
-      <c r="M30" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="N30" s="23"/>
-      <c r="O30" s="23"/>
-      <c r="P30" s="23"/>
-      <c r="Q30" s="23"/>
+      <c r="M30" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="N30" s="43"/>
+      <c r="O30" s="43"/>
+      <c r="P30" s="43"/>
+      <c r="Q30" s="43"/>
     </row>
     <row r="31" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="39" t="str">
+      <c r="B31" s="26" t="str">
         <f>LEFT(Table13[[#This Row],[Product ID]],2)</f>
         <v>24</v>
       </c>
-      <c r="C31" s="41" t="str">
+      <c r="C31" s="28" t="str">
         <f>RIGHT(Table13[[#This Row],[Product ID]],2)</f>
         <v>CA</v>
       </c>
-      <c r="D31" s="41" t="str">
+      <c r="D31" s="28" t="str">
         <f>MID(Table13[[#This Row],[Product ID]],4,3)</f>
         <v>MAY</v>
       </c>
-      <c r="E31" s="43" t="str">
+      <c r="E31" s="30" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Product Name]])))</f>
         <v>Fitness Tracker</v>
       </c>
-      <c r="F31" s="43" t="str">
+      <c r="F31" s="30" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Brand Name]])))</f>
         <v>Garmin</v>
       </c>
-      <c r="G31" s="36">
+      <c r="G31" s="23">
         <v>130</v>
       </c>
       <c r="H31" s="16">
         <v>5</v>
       </c>
-      <c r="I31" s="36">
+      <c r="I31" s="23">
         <f t="shared" si="0"/>
         <v>650</v>
       </c>
@@ -3473,49 +3464,49 @@
         <f>IF(Table13[[#This Row],[Selling Price ($)]]&gt;=500,"HIGH","STANDARD")</f>
         <v>HIGH</v>
       </c>
-      <c r="K31" s="46" t="str">
+      <c r="K31" s="33" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Category]])))</f>
         <v>Electronics</v>
       </c>
       <c r="L31" s="2"/>
-      <c r="N31" s="24" t="s">
+      <c r="N31" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="O31" s="24"/>
-      <c r="P31" s="24"/>
-      <c r="Q31" s="24"/>
+      <c r="O31" s="39"/>
+      <c r="P31" s="39"/>
+      <c r="Q31" s="39"/>
     </row>
     <row r="32" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="40" t="str">
+      <c r="B32" s="27" t="str">
         <f>LEFT(Table13[[#This Row],[Product ID]],2)</f>
         <v>02</v>
       </c>
-      <c r="C32" s="42" t="str">
+      <c r="C32" s="29" t="str">
         <f>RIGHT(Table13[[#This Row],[Product ID]],2)</f>
         <v>CA</v>
       </c>
-      <c r="D32" s="42" t="str">
+      <c r="D32" s="29" t="str">
         <f>MID(Table13[[#This Row],[Product ID]],4,3)</f>
         <v>DEC</v>
       </c>
-      <c r="E32" s="44" t="str">
+      <c r="E32" s="31" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Product Name]])))</f>
         <v>Jeans</v>
       </c>
-      <c r="F32" s="44" t="str">
+      <c r="F32" s="31" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Brand Name]])))</f>
         <v>Levi'S</v>
       </c>
-      <c r="G32" s="37">
+      <c r="G32" s="24">
         <v>50</v>
       </c>
       <c r="H32" s="17">
         <v>50</v>
       </c>
-      <c r="I32" s="37">
+      <c r="I32" s="24">
         <f t="shared" si="0"/>
         <v>2500</v>
       </c>
@@ -3523,49 +3514,49 @@
         <f>IF(Table13[[#This Row],[Selling Price ($)]]&gt;=500,"HIGH","STANDARD")</f>
         <v>HIGH</v>
       </c>
-      <c r="K32" s="46" t="str">
+      <c r="K32" s="33" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Category]])))</f>
         <v>Fashion</v>
       </c>
       <c r="L32" s="2"/>
-      <c r="N32" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="O32" s="25"/>
-      <c r="P32" s="25"/>
-      <c r="Q32" s="25"/>
+      <c r="N32" s="35" t="s">
+        <v>69</v>
+      </c>
+      <c r="O32" s="35"/>
+      <c r="P32" s="35"/>
+      <c r="Q32" s="35"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="40" t="str">
+      <c r="B33" s="27" t="str">
         <f>LEFT(Table13[[#This Row],[Product ID]],2)</f>
         <v>09</v>
       </c>
-      <c r="C33" s="42" t="str">
+      <c r="C33" s="29" t="str">
         <f>RIGHT(Table13[[#This Row],[Product ID]],2)</f>
         <v>FR</v>
       </c>
-      <c r="D33" s="42" t="str">
+      <c r="D33" s="29" t="str">
         <f>MID(Table13[[#This Row],[Product ID]],4,3)</f>
         <v>JUL</v>
       </c>
-      <c r="E33" s="44" t="str">
+      <c r="E33" s="31" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Product Name]])))</f>
         <v>Watch</v>
       </c>
-      <c r="F33" s="44" t="str">
+      <c r="F33" s="31" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Brand Name]])))</f>
         <v>Casio</v>
       </c>
-      <c r="G33" s="37">
+      <c r="G33" s="24">
         <v>100</v>
       </c>
       <c r="H33" s="17">
         <v>20</v>
       </c>
-      <c r="I33" s="37">
+      <c r="I33" s="24">
         <f t="shared" si="0"/>
         <v>2000</v>
       </c>
@@ -3573,18 +3564,17 @@
         <f>IF(Table13[[#This Row],[Selling Price ($)]]&gt;=500,"HIGH","STANDARD")</f>
         <v>HIGH</v>
       </c>
-      <c r="K33" s="46" t="str">
+      <c r="K33" s="33" t="str">
         <f ca="1">PROPER(TRIM(CLEAN(Table13[[#This Row],[Category]])))</f>
         <v>Accessories</v>
       </c>
       <c r="L33" s="2"/>
-      <c r="N33" s="27">
-        <f>I42</f>
+      <c r="N33" s="41">
         <v>36000</v>
       </c>
-      <c r="O33" s="27"/>
-      <c r="P33" s="27"/>
-      <c r="Q33" s="27"/>
+      <c r="O33" s="41"/>
+      <c r="P33" s="41"/>
+      <c r="Q33" s="41"/>
     </row>
     <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="18"/>
@@ -3596,77 +3586,77 @@
         <v>32</v>
       </c>
       <c r="F34" s="22"/>
-      <c r="G34" s="38"/>
-      <c r="H34" s="45">
+      <c r="G34" s="25"/>
+      <c r="H34" s="32">
         <f>SUM(Table13[Quantity])</f>
         <v>840</v>
       </c>
-      <c r="I34" s="38">
+      <c r="I34" s="25">
         <f>SUM(Table13[Selling Price ($)])</f>
         <v>264200</v>
       </c>
       <c r="J34" s="22"/>
-      <c r="K34" s="47"/>
+      <c r="K34" s="34"/>
       <c r="L34" s="2"/>
     </row>
     <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L35" s="2"/>
       <c r="M35" s="14" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M37" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="N37" s="23"/>
-      <c r="O37" s="23"/>
-      <c r="P37" s="23"/>
-      <c r="Q37" s="23"/>
+      <c r="M37" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="N37" s="43"/>
+      <c r="O37" s="43"/>
+      <c r="P37" s="43"/>
+      <c r="Q37" s="43"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H38" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="I38" s="9">
         <f>AVERAGE(Table13[Selling Price ($)])</f>
         <v>8256.25</v>
       </c>
       <c r="J38" s="11"/>
-      <c r="N38" s="24" t="s">
+      <c r="N38" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="O38" s="24"/>
-      <c r="P38" s="24"/>
-      <c r="Q38" s="24"/>
+      <c r="O38" s="39"/>
+      <c r="P38" s="39"/>
+      <c r="Q38" s="39"/>
     </row>
     <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N39" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="O39" s="25"/>
-      <c r="P39" s="25"/>
-      <c r="Q39" s="25"/>
+      <c r="N39" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="O39" s="35"/>
+      <c r="P39" s="35"/>
+      <c r="Q39" s="35"/>
     </row>
     <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H40" s="9" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I40" s="9">
         <f>MIN(Table13[Selling Price ($)])</f>
         <v>150</v>
       </c>
       <c r="J40" s="11"/>
-      <c r="N40" s="26"/>
-      <c r="O40" s="26"/>
-      <c r="P40" s="26"/>
-      <c r="Q40" s="26"/>
+      <c r="N40" s="47"/>
+      <c r="O40" s="47"/>
+      <c r="P40" s="47"/>
+      <c r="Q40" s="47"/>
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H42" s="9" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="I42" s="9">
         <f>MAX(Table13[Selling Price ($)])</f>
@@ -3677,7 +3667,7 @@
     <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H44" s="9" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="I44" s="9">
         <f ca="1">SUMIF(Table13[[#Headers],[#Data],[Category]],K2,Table13[[#Headers],[#Data],[Selling Price ($)]])</f>
@@ -3688,7 +3678,7 @@
     <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H46" s="9" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="I46" s="9">
         <f>COUNTIF(Table13[Price ($)],"&lt;=100")</f>
@@ -4652,6 +4642,29 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="M37:Q37"/>
+    <mergeCell ref="N38:Q38"/>
+    <mergeCell ref="N39:Q39"/>
+    <mergeCell ref="N40:Q40"/>
+    <mergeCell ref="N27:Q27"/>
+    <mergeCell ref="N28:Q28"/>
+    <mergeCell ref="M30:Q30"/>
+    <mergeCell ref="N31:Q31"/>
+    <mergeCell ref="N32:Q32"/>
+    <mergeCell ref="N33:Q33"/>
+    <mergeCell ref="N26:Q26"/>
+    <mergeCell ref="T26:Z26"/>
+    <mergeCell ref="N16:Q16"/>
+    <mergeCell ref="T16:Z16"/>
+    <mergeCell ref="T17:Z17"/>
+    <mergeCell ref="M18:Q18"/>
+    <mergeCell ref="T18:Z18"/>
+    <mergeCell ref="N19:Q19"/>
+    <mergeCell ref="N20:Q20"/>
+    <mergeCell ref="N21:Q21"/>
+    <mergeCell ref="S23:Z23"/>
+    <mergeCell ref="T24:Z24"/>
+    <mergeCell ref="M25:Q25"/>
     <mergeCell ref="N15:Q15"/>
     <mergeCell ref="S15:Z15"/>
     <mergeCell ref="M5:Q6"/>
@@ -4665,29 +4678,6 @@
     <mergeCell ref="M13:Q13"/>
     <mergeCell ref="T13:Z13"/>
     <mergeCell ref="N14:Q14"/>
-    <mergeCell ref="N26:Q26"/>
-    <mergeCell ref="T26:Z26"/>
-    <mergeCell ref="N16:Q16"/>
-    <mergeCell ref="T16:Z16"/>
-    <mergeCell ref="T17:Z17"/>
-    <mergeCell ref="M18:Q18"/>
-    <mergeCell ref="T18:Z18"/>
-    <mergeCell ref="N19:Q19"/>
-    <mergeCell ref="N20:Q20"/>
-    <mergeCell ref="N21:Q21"/>
-    <mergeCell ref="S23:Z23"/>
-    <mergeCell ref="T24:Z24"/>
-    <mergeCell ref="M25:Q25"/>
-    <mergeCell ref="M37:Q37"/>
-    <mergeCell ref="N38:Q38"/>
-    <mergeCell ref="N39:Q39"/>
-    <mergeCell ref="N40:Q40"/>
-    <mergeCell ref="N27:Q27"/>
-    <mergeCell ref="N28:Q28"/>
-    <mergeCell ref="M30:Q30"/>
-    <mergeCell ref="N31:Q31"/>
-    <mergeCell ref="N32:Q32"/>
-    <mergeCell ref="N33:Q33"/>
   </mergeCells>
   <conditionalFormatting sqref="I2:J33">
     <cfRule type="colorScale" priority="1">
@@ -4701,9 +4691,11 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
+  <pageSetup paperSize="8" orientation="landscape" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>